--- a/artfynd/A 11604-2026 artfynd.xlsx
+++ b/artfynd/A 11604-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,130 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131455468</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91838</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hjortkullen, Hjorten, Törnsfall, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>591161</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6407832</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst 3 Talltickor på samma tall</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11604-2026 artfynd.xlsx
+++ b/artfynd/A 11604-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,6 +921,125 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131466931</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58046</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hjortkullen, Hjorten, Törnsfall, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>591122</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6407877</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11604-2026 artfynd.xlsx
+++ b/artfynd/A 11604-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>131455468</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>131466931</v>
       </c>
       <c r="B4" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,7 +958,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 11604-2026 artfynd.xlsx
+++ b/artfynd/A 11604-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>131455468</v>
       </c>
       <c r="B3" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>131466931</v>
       </c>
       <c r="B4" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11604-2026 artfynd.xlsx
+++ b/artfynd/A 11604-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>131455468</v>
       </c>
       <c r="B3" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>131466931</v>
       </c>
       <c r="B4" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11604-2026 artfynd.xlsx
+++ b/artfynd/A 11604-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>131455468</v>
       </c>
       <c r="B3" t="n">
-        <v>91843</v>
+        <v>91849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>131466931</v>
       </c>
       <c r="B4" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11604-2026 artfynd.xlsx
+++ b/artfynd/A 11604-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>131455468</v>
       </c>
       <c r="B3" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>131466931</v>
       </c>
       <c r="B4" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11604-2026 artfynd.xlsx
+++ b/artfynd/A 11604-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,7 +802,7 @@
         <v>131455468</v>
       </c>
       <c r="B3" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>131466931</v>
       </c>
       <c r="B4" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,6 +1043,134 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131806094</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58061</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hjortkullen, Hjorten, Törnsfall, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>591145</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6407848</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 st talltitor som varnade</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11604-2026 artfynd.xlsx
+++ b/artfynd/A 11604-2026 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>131455468</v>
       </c>
       <c r="B3" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>131466931</v>
       </c>
       <c r="B4" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>131806094</v>
       </c>
       <c r="B5" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 11604-2026 artfynd.xlsx
+++ b/artfynd/A 11604-2026 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>131806094</v>
       </c>
       <c r="B5" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>131806076</v>
       </c>
       <c r="B6" t="n">
-        <v>96685</v>
+        <v>96688</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 11604-2026 artfynd.xlsx
+++ b/artfynd/A 11604-2026 artfynd.xlsx
@@ -675,64 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121609810</v>
+        <v>131806076</v>
       </c>
       <c r="B2" t="n">
-        <v>90762</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnsjön, Sm</t>
+          <t>Hjortkullen, Hjorten, Törnsfall, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591175</v>
+        <v>591202</v>
       </c>
       <c r="R2" t="n">
-        <v>6407834</v>
+        <v>6407861</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,22 +783,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131455468</v>
+        <v>121609810</v>
       </c>
       <c r="B3" t="n">
-        <v>91867</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,17 +837,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hjortkullen, Hjorten, Törnsfall, Sm</t>
+          <t>Kvarnsjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591161</v>
+        <v>591175</v>
       </c>
       <c r="R3" t="n">
-        <v>6407832</v>
+        <v>6407834</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,27 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Minst 3 Talltickor på samma tall</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131466931</v>
+        <v>131455468</v>
       </c>
       <c r="B4" t="n">
-        <v>58073</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,50 +925,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hjortkullen, Hjorten, Törnsfall, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591122</v>
+        <v>591161</v>
       </c>
       <c r="R4" t="n">
-        <v>6407877</v>
+        <v>6407832</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,22 +990,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Minst 3 Talltickor på samma tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,6 +1019,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1046,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131806094</v>
+        <v>131466931</v>
       </c>
       <c r="B5" t="n">
-        <v>58109</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1068,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1088,7 +1080,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1097,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591145</v>
+        <v>591122</v>
       </c>
       <c r="R5" t="n">
-        <v>6407848</v>
+        <v>6407877</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1127,27 +1119,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>11:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2 st talltitor som varnade</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1174,60 +1161,64 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131806076</v>
+        <v>131806094</v>
       </c>
       <c r="B6" t="n">
-        <v>96688</v>
+        <v>58136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hjortkullen, Hjorten, Törnsfall, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591202</v>
+        <v>591145</v>
       </c>
       <c r="R6" t="n">
-        <v>6407861</v>
+        <v>6407848</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1269,13 +1260,17 @@
           <t>11:30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 st talltitor som varnade</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
